--- a/ExperimentalResults/Result.xlsx
+++ b/ExperimentalResults/Result.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csflhe\Desktop\NeckPass和RenderLeaks的实验数据和上传到匿名\匿名github\NeckPass\ExperimentalResults\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\data_backup\backup\科研资料\neckpass\neckpass提交github\NeckPass\ExperimentalResults\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11A79B9-5811-4958-BB2E-9B316C4DD86A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B09E024B-9A63-44AE-8F43-82790A725771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="15000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19080" yWindow="-120" windowWidth="19440" windowHeight="15000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="8.2" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="118">
   <si>
     <t>No</t>
   </si>
@@ -386,6 +386,12 @@
   </si>
   <si>
     <t>8.3.6. Impacts of Heart Rate Variations</t>
+  </si>
+  <si>
+    <t>AUC</t>
+  </si>
+  <si>
+    <t>EER</t>
   </si>
 </sst>
 </file>
@@ -442,7 +448,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -481,12 +487,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -769,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" style="1" customWidth="1"/>
@@ -1296,6 +1296,22 @@
       <c r="F26" s="5">
         <f t="shared" si="0"/>
         <v>0.96347916666666666</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B28" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0.98406099999999996</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B29" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" s="5">
+        <v>4.1050000000000003E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1716,8 +1732,7 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="14"/>
-      <c r="C18" s="15"/>
+      <c r="A18" s="6"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
